--- a/data/trans_camb/P44-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P44-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 5,69</t>
+          <t>-0,41; 5,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,96; 32,57</t>
+          <t>23,17; 32,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 3,95</t>
+          <t>-1,1; 4,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,22; 23,12</t>
+          <t>17,28; 23,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 3,91</t>
+          <t>-0,0; 4,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,3; 25,59</t>
+          <t>20,69; 25,49</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 101,04</t>
+          <t>-5,07; 99,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>246,31; 564,35</t>
+          <t>244,14; 558,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 74,45</t>
+          <t>-15,57; 71,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220,82; 425,49</t>
+          <t>215,4; 426,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 62,99</t>
+          <t>-2,17; 67,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>249,86; 428,33</t>
+          <t>265,06; 437,14</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 4,11</t>
+          <t>-4,51; 4,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,6; 66,64</t>
+          <t>21,62; 64,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 1,38</t>
+          <t>-5,86; 1,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 23,57</t>
+          <t>3,82; 23,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 1,64</t>
+          <t>-3,79; 1,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,63; 50,06</t>
+          <t>16,24; 50,75</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,74; 45,88</t>
+          <t>-30,35; 46,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>173,78; 753,22</t>
+          <t>170,38; 722,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-55,84; 27,38</t>
+          <t>-57,29; 21,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41,64; 362,5</t>
+          <t>45,1; 356,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,7; 20,07</t>
+          <t>-33,54; 18,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>151,15; 577,0</t>
+          <t>155,44; 605,94</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 12,85</t>
+          <t>-7,03; 12,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,24; 38,5</t>
+          <t>18,15; 37,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 5,12</t>
+          <t>-20,86; 4,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 29,54</t>
+          <t>6,14; 29,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 6,51</t>
+          <t>-9,31; 6,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,87; 32,29</t>
+          <t>17,81; 32,28</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,79; 143,91</t>
+          <t>-35,55; 145,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79,93; 403,22</t>
+          <t>77,06; 407,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-67,93; 58,49</t>
+          <t>-66,94; 45,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,72; 271,1</t>
+          <t>19,93; 275,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,21; 54,1</t>
+          <t>-41,73; 61,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,99; 278,12</t>
+          <t>75,53; 286,11</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 4,67</t>
+          <t>-0,37; 4,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,06; 57,6</t>
+          <t>25,69; 54,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,91</t>
+          <t>-2,13; 2,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,9; 23,36</t>
+          <t>9,54; 23,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,74</t>
+          <t>-0,52; 2,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,68; 40,36</t>
+          <t>20,82; 40,97</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 57,75</t>
+          <t>-3,36; 58,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>254,38; 684,79</t>
+          <t>248,71; 620,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,36; 30,36</t>
+          <t>-24,59; 30,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>145,99; 346,95</t>
+          <t>136,34; 356,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 36,56</t>
+          <t>-6,03; 33,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>232,11; 485,57</t>
+          <t>235,16; 486,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P44-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P44-Estudios-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27,87</t>
+          <t>27,43</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,15</t>
+          <t>20,68</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,13</t>
+          <t>23,28</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 5,88</t>
+          <t>-0,51; 6,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,17; 32,56</t>
+          <t>22,85; 31,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 4,01</t>
+          <t>-0,91; 4,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,28; 23,25</t>
+          <t>17,67; 23,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 4,05</t>
+          <t>-0,13; 4,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,69; 25,49</t>
+          <t>20,72; 25,77</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>374,27%</t>
+          <t>368,27%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>308,92%</t>
+          <t>317,14%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>335,97%</t>
+          <t>338,23%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 99,71</t>
+          <t>-6,43; 103,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>244,14; 558,62</t>
+          <t>243,86; 549,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 71,49</t>
+          <t>-12,71; 79,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>215,4; 426,37</t>
+          <t>223,34; 431,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 67,6</t>
+          <t>-1,84; 68,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>265,06; 437,14</t>
+          <t>260,71; 450,28</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>38,55</t>
+          <t>22,58</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,9</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,69</t>
+          <t>22,49</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 4,09</t>
+          <t>-4,15; 4,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,62; 64,87</t>
+          <t>18,24; 27,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 1,1</t>
+          <t>-5,72; 1,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 23,5</t>
+          <t>18,2; 26,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,57</t>
+          <t>-3,64; 1,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,24; 50,75</t>
+          <t>19,31; 25,43</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>338,33%</t>
+          <t>198,19%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203,18%</t>
+          <t>287,53%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>285,14%</t>
+          <t>231,6%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,35; 46,26</t>
+          <t>-28,48; 54,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>170,38; 722,13</t>
+          <t>124,52; 323,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,29; 21,0</t>
+          <t>-55,67; 26,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,1; 356,89</t>
+          <t>161,68; 485,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,54; 18,8</t>
+          <t>-31,95; 24,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>155,44; 605,94</t>
+          <t>161,81; 326,02</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29,77</t>
+          <t>29,08</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,91</t>
+          <t>19,32</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,29</t>
+          <t>25,03</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 12,31</t>
+          <t>-7,28; 12,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,15; 37,68</t>
+          <t>19,19; 37,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,86; 4,59</t>
+          <t>-20,37; 4,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 29,73</t>
+          <t>5,9; 29,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 6,65</t>
+          <t>-9,24; 6,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,81; 32,28</t>
+          <t>17,13; 31,89</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>200,4%</t>
+          <t>195,77%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>151,27%</t>
+          <t>149,72%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 145,29</t>
+          <t>-37,54; 126,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>77,06; 407,91</t>
+          <t>84,13; 461,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-66,94; 45,59</t>
+          <t>-69,38; 41,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,93; 275,66</t>
+          <t>19,74; 271,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,73; 61,13</t>
+          <t>-42,45; 57,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75,53; 286,11</t>
+          <t>73,57; 288,63</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>36,08</t>
+          <t>26,53</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19,17</t>
+          <t>22,9</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,48</t>
+          <t>24,69</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 4,77</t>
+          <t>-0,18; 4,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,69; 54,91</t>
+          <t>23,43; 29,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,03</t>
+          <t>-2,14; 2,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,54; 23,31</t>
+          <t>20,8; 25,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,57</t>
+          <t>-0,45; 2,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,82; 40,97</t>
+          <t>22,91; 26,68</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>378,0%</t>
+          <t>277,96%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>257,7%</t>
+          <t>307,82%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>327,72%</t>
+          <t>294,46%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 58,49</t>
+          <t>-2,03; 59,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>248,71; 620,48</t>
+          <t>211,79; 371,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-24,59; 30,72</t>
+          <t>-24,66; 34,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>136,34; 356,03</t>
+          <t>236,17; 401,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 33,67</t>
+          <t>-4,94; 35,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>235,16; 486,87</t>
+          <t>243,48; 362,57</t>
         </is>
       </c>
     </row>
